--- a/results/Int Task Remove ACC 0.6/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.6/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.02366092013567846</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008312165669017622</v>
+        <v>0.008307254077662024</v>
       </c>
       <c r="F3" t="n">
         <v>0.001902275023324324</v>
@@ -1169,7 +1169,7 @@
         <v>-0.001230541605065018</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003433503663983295</v>
+        <v>0.0003482141796279015</v>
       </c>
       <c r="J3" t="n">
         <v>0.01716609600385098</v>
@@ -1187,7 +1187,7 @@
         <v>0.01989604711745225</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004324780525695698</v>
+        <v>0.004324649176393574</v>
       </c>
       <c r="P3" t="n">
         <v>0.01202692733793122</v>
@@ -1196,7 +1196,7 @@
         <v>0.004548021094942578</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005075636097603075</v>
+        <v>0.00508519175933265</v>
       </c>
       <c r="S3" t="n">
         <v>0.3342125334402991</v>
@@ -1208,7 +1208,7 @@
         <v>0.2594304711358102</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0003480451911320481</v>
+        <v>0.0003480959454917887</v>
       </c>
       <c r="W3" t="n">
         <v>0.002825566658156801</v>
@@ -1253,7 +1253,7 @@
         <v>0.07646101367537844</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.07049200936733074</v>
+        <v>0.07047619492347203</v>
       </c>
       <c r="AL3" t="n">
         <v>-0.0007940477237597165</v>
@@ -1304,7 +1304,7 @@
         <v>0.007770050669692169</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.001247060570910957</v>
+        <v>0.001242196757681385</v>
       </c>
       <c r="BC3" t="n">
         <v>0.0009542334528356945</v>
@@ -1319,7 +1319,7 @@
         <v>0.020339243239872</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.02775491609046303</v>
+        <v>0.02775000449910743</v>
       </c>
       <c r="BH3" t="n">
         <v>0.0002379077703424848</v>
@@ -1355,7 +1355,7 @@
         <v>0.007143593492040304</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0006894975608629993</v>
+        <v>-0.0006842260795767573</v>
       </c>
       <c r="BT3" t="n">
         <v>0.001117507622675728</v>
@@ -1428,7 +1428,7 @@
         <v>0.03332133088836218</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03258490444735448</v>
+        <v>0.03258822497210533</v>
       </c>
       <c r="F4" t="n">
         <v>0.007529156062100633</v>
@@ -1440,7 +1440,7 @@
         <v>0.01503165341811435</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001403153573093202</v>
+        <v>0.001406220684877594</v>
       </c>
       <c r="J4" t="n">
         <v>0.02903231884368739</v>
@@ -1458,7 +1458,7 @@
         <v>0.0531780002378472</v>
       </c>
       <c r="O4" t="n">
-        <v>0.021753966032254</v>
+        <v>0.02176149703102431</v>
       </c>
       <c r="P4" t="n">
         <v>0.02865635230964913</v>
@@ -1467,7 +1467,7 @@
         <v>0.0163643907889367</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02256539379349016</v>
+        <v>0.02255753924190593</v>
       </c>
       <c r="S4" t="n">
         <v>0.134729506308821</v>
@@ -1479,7 +1479,7 @@
         <v>0.08987744719221588</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00140924224312535</v>
+        <v>0.001404012535575247</v>
       </c>
       <c r="W4" t="n">
         <v>0.01336503033373111</v>
@@ -1524,7 +1524,7 @@
         <v>0.09101288224426017</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0881202125639599</v>
+        <v>0.08813977859944878</v>
       </c>
       <c r="AL4" t="n">
         <v>0.001365566866470312</v>
@@ -1575,7 +1575,7 @@
         <v>0.02416890784083003</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.03798904429220409</v>
+        <v>0.03798543986247818</v>
       </c>
       <c r="BC4" t="n">
         <v>0.003811062146913828</v>
@@ -1590,7 +1590,7 @@
         <v>0.04147720800198729</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.03883524365300387</v>
+        <v>0.03883515765443198</v>
       </c>
       <c r="BH4" t="n">
         <v>0.0005087631844362853</v>
@@ -1626,7 +1626,7 @@
         <v>0.01647535563104679</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01186359373106402</v>
+        <v>0.01185907814441759</v>
       </c>
       <c r="BT4" t="n">
         <v>0.002178811588997204</v>
@@ -1729,7 +1729,7 @@
         <v>-0.02047128129602349</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.03127147766323023</v>
+        <v>-0.03132056946489935</v>
       </c>
       <c r="P5" t="n">
         <v>-0.03646496815286625</v>
@@ -1970,7 +1970,7 @@
         <v>0.002801840523446972</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01008267888600861</v>
+        <v>-0.0101195158211756</v>
       </c>
       <c r="F6" t="n">
         <v>-0.003014481464195917</v>
@@ -2000,7 +2000,7 @@
         <v>-0.0034267685835811</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.002348783174731678</v>
+        <v>-0.00233683859756971</v>
       </c>
       <c r="P6" t="n">
         <v>-0.004606480971178533</v>
@@ -2009,7 +2009,7 @@
         <v>0.001997103286209936</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.01779659863498589</v>
+        <v>-0.01777270948066196</v>
       </c>
       <c r="S6" t="n">
         <v>0.2341477862495857</v>
@@ -2292,7 +2292,7 @@
         <v>0.2701840300782107</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001251992269167501</v>
+        <v>0.0001493421530393946</v>
       </c>
       <c r="W7" t="n">
         <v>0.002727796549272632</v>
@@ -2403,7 +2403,7 @@
         <v>0.01644256364753257</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.03145043569314347</v>
+        <v>0.03142587773636547</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -2524,7 +2524,7 @@
         <v>0.008657828915468407</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001426348668249355</v>
+        <v>0.001438508201323285</v>
       </c>
       <c r="J8" t="n">
         <v>0.04036349624754881</v>
@@ -2563,7 +2563,7 @@
         <v>0.3345113083892888</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001462182399735268</v>
+        <v>0.001426348668249355</v>
       </c>
       <c r="W8" t="n">
         <v>0.007424739100828217</v>
